--- a/Bodydot Payment - Month YEAR.xlsx
+++ b/Bodydot Payment - Month YEAR.xlsx
@@ -774,21 +774,9 @@
         </is>
       </c>
       <c r="B3" s="23" t="n"/>
-      <c r="C3" s="43" t="n"/>
-      <c r="D3" s="15" t="n"/>
-    </row>
-    <row r="4" ht="47.75" customHeight="1">
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="26" t="n"/>
-      <c r="D4" s="1" t="n"/>
-    </row>
-    <row r="5" ht="47.75" customHeight="1">
-      <c r="A5" s="38" t="n"/>
-      <c r="B5" s="38" t="n"/>
-      <c r="C5" s="39" t="n"/>
-      <c r="D5" s="40" t="n"/>
-      <c r="F5" s="5" t="n"/>
-    </row>
+    </row>
+    <row r="4" ht="47.75" customHeight="1"/>
+    <row r="5" ht="47.75" customHeight="1"/>
     <row r="6" ht="49.25" customHeight="1">
       <c r="A6" s="56" t="inlineStr">
         <is>
@@ -796,14 +784,12 @@
         </is>
       </c>
       <c r="B6" s="38" t="n"/>
-      <c r="C6" s="42" t="n"/>
       <c r="D6" s="56" t="inlineStr">
         <is>
           <t>BODY MOTIONS BRANCHES</t>
         </is>
       </c>
       <c r="E6" s="38" t="n"/>
-      <c r="F6" s="5" t="n"/>
       <c r="G6" s="57" t="inlineStr">
         <is>
           <t>TOTAL GYMS</t>
@@ -823,7 +809,6 @@
           <t>Total Tests</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n"/>
       <c r="D7" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">CLUB NAME
@@ -859,7 +844,6 @@
           <t>إجمالي الاختبارات</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n"/>
       <c r="D8" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">اسم النادي
@@ -890,7 +874,6 @@
         </is>
       </c>
       <c r="B9" s="21" t="n"/>
-      <c r="C9" s="11" t="n"/>
       <c r="D9" s="25" t="inlineStr">
         <is>
           <t>RUH - Al Sahafa</t>
@@ -908,11 +891,6 @@
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="10" t="n"/>
       <c r="G10" s="25" t="inlineStr">
         <is>
           <t>Body Masters</t>
@@ -923,272 +901,44 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="10" t="n"/>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="10" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="10" t="n"/>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="10" t="n"/>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="10" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="10" t="n"/>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="10" t="n"/>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="10" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="10" t="n"/>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="10" t="n"/>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="10" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="10" t="n"/>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="10" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="10" t="n"/>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="10" t="n"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="10" t="n"/>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="10" t="n"/>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="10" t="n"/>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="10" t="n"/>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="10" t="n"/>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="10" t="n"/>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="10" t="n"/>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="10" t="n"/>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="10" t="n"/>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="10" t="n"/>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="10" t="n"/>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="10" t="n"/>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="10" t="n"/>
-    </row>
+    <row r="11" ht="16" customHeight="1"/>
+    <row r="12" ht="16" customHeight="1"/>
+    <row r="13" ht="16" customHeight="1"/>
+    <row r="14" ht="16" customHeight="1"/>
+    <row r="15" ht="16" customHeight="1"/>
+    <row r="16" ht="16" customHeight="1"/>
+    <row r="17" ht="16" customHeight="1"/>
+    <row r="18" ht="16" customHeight="1"/>
+    <row r="19" ht="16" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1"/>
+    <row r="21" ht="16" customHeight="1"/>
+    <row r="22" ht="16" customHeight="1"/>
+    <row r="23" ht="16" customHeight="1"/>
+    <row r="24" ht="16" customHeight="1"/>
+    <row r="25" ht="16" customHeight="1"/>
+    <row r="26" ht="16" customHeight="1"/>
+    <row r="27" ht="16" customHeight="1"/>
+    <row r="28" ht="16" customHeight="1"/>
+    <row r="29" ht="16" customHeight="1"/>
+    <row r="30" ht="16" customHeight="1"/>
+    <row r="31" ht="16" customHeight="1"/>
+    <row r="32" ht="16" customHeight="1"/>
+    <row r="33" ht="16" customHeight="1"/>
+    <row r="34" ht="16" customHeight="1"/>
+    <row r="35" ht="16" customHeight="1"/>
+    <row r="36" ht="16" customHeight="1"/>
+    <row r="37" ht="16" customHeight="1"/>
+    <row r="38" ht="16" customHeight="1"/>
+    <row r="39" ht="16" customHeight="1"/>
+    <row r="40" ht="16" customHeight="1"/>
+    <row r="41" ht="16" customHeight="1"/>
+    <row r="42" ht="16" customHeight="1"/>
+    <row r="43" ht="16" customHeight="1"/>
+    <row r="44" ht="16" customHeight="1"/>
+    <row r="45" ht="16" customHeight="1"/>
+    <row r="46" ht="16" customHeight="1"/>
+    <row r="47" ht="16" customHeight="1"/>
+    <row r="48" ht="16" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="D6:E6"/>

--- a/Bodydot Payment - Month YEAR.xlsx
+++ b/Bodydot Payment - Month YEAR.xlsx
@@ -12,8 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'REPORT'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'REPORT'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Body Masters - RUH - Al Aarid'!$B$1:$H$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'REPORT'!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -2624,6 +2623,14 @@
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="41"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;G</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
